--- a/www/ig/fhir/tddui/CodeSystem-tddui-discriminator.xlsx
+++ b/www/ig/fhir/tddui/CodeSystem-tddui-discriminator.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T14:53:05+00:00</t>
+    <t>2026-03-16T15:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/www/ig/fhir/tddui/CodeSystem-tddui-discriminator.xlsx
+++ b/www/ig/fhir/tddui/CodeSystem-tddui-discriminator.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T15:53:20+00:00</t>
+    <t>2026-07-22T14:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>11</t>
   </si>
   <si>
     <t>Level</t>
@@ -181,6 +181,30 @@
   </si>
   <si>
     <t>Permet de compléter ou éclairer la description de l'attente.</t>
+  </si>
+  <si>
+    <t>demandeOrientation</t>
+  </si>
+  <si>
+    <t>Pièce jointe composant la demande d'orientation.</t>
+  </si>
+  <si>
+    <t>depotPoste</t>
+  </si>
+  <si>
+    <t>Preuve du dépôt de la poste.</t>
+  </si>
+  <si>
+    <t>reponseOrientation</t>
+  </si>
+  <si>
+    <t>Réponse de la CDAPH à la demande d'orientation.</t>
+  </si>
+  <si>
+    <t>pieceComplementaire</t>
+  </si>
+  <si>
+    <t>Pièce(s) complémentaire(s) à la demande d'orientation.</t>
   </si>
 </sst>
 </file>
@@ -492,7 +516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -593,6 +617,54 @@
       </c>
       <c r="D8" s="2"/>
     </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
